--- a/contacts.xlsx
+++ b/contacts.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\bot kpanou\bot admin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8940"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4575"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,14 +30,14 @@
     <t>Aboulle Dev</t>
   </si>
   <si>
-    <t>aboulledev@gmail.com</t>
+    <t>abdoulledev@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -49,6 +49,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -86,16 +94,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -398,26 +409,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>